--- a/data/trans_orig/P15B_3_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2007 (tasa de respuesta: 51,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24013</t>
+          <t>23816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32051</t>
+          <t>31819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33622</t>
+          <t>33305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>24888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17372</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>29037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43022</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23313</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,62 +2140,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1686</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6142</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2046</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6467</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,97 +2448,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1423</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1556</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1629</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2791,97 +2791,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1567</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20555</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26520</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>50354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37066</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63918</t>
+          <t>62093</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71974</t>
+          <t>72723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93407</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>76731</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>89103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152965</t>
+          <t>154790</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>179817</t>
+          <t>180116</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2012 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>49174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56901</t>
+          <t>56891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27696</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79907</t>
+          <t>79152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88456</t>
+          <t>88476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>14355</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53596</t>
+          <t>52644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67762</t>
+          <t>67965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27622</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36876</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84817</t>
+          <t>85185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102825</t>
+          <t>102940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>21751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23974</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48443</t>
+          <t>48594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>23301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61980</t>
+          <t>61391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76606</t>
+          <t>76579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26980</t>
+          <t>26392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>24314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>33925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43564</t>
+          <t>42476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59002</t>
+          <t>59523</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,47%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36242</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41265</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51587</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -5427,97 +5427,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1894</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40735</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42629</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5770,97 +5770,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5391</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>9,95%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1183</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5902</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5229</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5885</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48290</t>
+          <t>48801</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70339</t>
+          <t>70995</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49496</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77841</t>
+          <t>76648</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23649</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60244</t>
+          <t>59450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94567</t>
+          <t>94118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>209131</t>
+          <t>210324</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>237476</t>
+          <t>238230</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>231756</t>
+          <t>232272</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248464</t>
+          <t>248844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>447810</t>
+          <t>448259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>482133</t>
+          <t>482927</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37909</t>
+          <t>37883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53018</t>
+          <t>54154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60254</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24978</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31086</t>
+          <t>31418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43044</t>
+          <t>43237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48558</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62805</t>
+          <t>62865</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21521</t>
+          <t>20435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>32285</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>42859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55931</t>
+          <t>56042</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12538</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16736</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16393</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26261</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23489</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36582</t>
+          <t>36520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48422</t>
+          <t>48288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9803</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29351</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>34758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>43273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -8406,97 +8406,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1715</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8749,97 +8749,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1515</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2463</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2174</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53523</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>55697</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>40329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22882</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>157440</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>177556</t>
+          <t>177318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>168571</t>
+          <t>169496</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>183307</t>
+          <t>183533</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332597</t>
+          <t>331998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>357507</t>
+          <t>357533</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>14656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35964</t>
+          <t>36213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16428</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18802</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23438</t>
+          <t>23710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37663</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21422</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32605</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21843</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>27307</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45533</t>
+          <t>46106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58783</t>
+          <t>58532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23364</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29116</t>
+          <t>29991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42556</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23901</t>
+          <t>23801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>28702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55790</t>
+          <t>55756</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70085</t>
+          <t>70105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9578</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>21038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24076</t>
+          <t>23978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26004</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32279</t>
+          <t>32243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42998</t>
+          <t>43283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>54336</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30425</t>
+          <t>29853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44798</t>
+          <t>44490</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11728,97 +11728,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72744</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>34267</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60830</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>24561</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49842</t>
+          <t>47614</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81321</t>
+          <t>78884</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>138300</t>
+          <t>137991</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>165532</t>
+          <t>164863</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>188532</t>
+          <t>189042</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203530</t>
+          <t>203576</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331412</t>
+          <t>333849</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>362891</t>
+          <t>365119</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15B_3_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P15B_3_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31819</t>
+          <t>31906</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>42431</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29037</t>
+          <t>28936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>28971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>43259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>17432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9857</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,09%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>29880</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>37616</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>62717</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72723</t>
+          <t>71266</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92869</t>
+          <t>93197</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>76808</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>89103</t>
+          <t>89342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>154790</t>
+          <t>154166</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>180116</t>
+          <t>179267</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>11321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49174</t>
+          <t>49094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56891</t>
+          <t>57045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79152</t>
+          <t>79043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88476</t>
+          <t>88364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29676</t>
+          <t>30278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17409</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35164</t>
+          <t>34881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52644</t>
+          <t>52042</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67965</t>
+          <t>68056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>27286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85185</t>
+          <t>85468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102940</t>
+          <t>103300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21751</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9375</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>24722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>34958</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48594</t>
+          <t>48134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>23311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61391</t>
+          <t>61232</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76579</t>
+          <t>76744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29703</t>
+          <t>28565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26392</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24314</t>
+          <t>23927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33925</t>
+          <t>33964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>43614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59523</t>
+          <t>59080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>13097</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>37283</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>41581</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51570</t>
+          <t>51618</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48801</t>
+          <t>48313</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70995</t>
+          <t>69566</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>48908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>76648</t>
+          <t>76630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59450</t>
+          <t>60449</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94118</t>
+          <t>92848</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>210324</t>
+          <t>210342</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>238230</t>
+          <t>238064</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>232272</t>
+          <t>232380</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248844</t>
+          <t>248400</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>448259</t>
+          <t>449529</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>482927</t>
+          <t>481928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37883</t>
+          <t>37865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54154</t>
+          <t>53153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>60242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>24120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31418</t>
+          <t>31845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43237</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>21685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48829</t>
+          <t>49416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62865</t>
+          <t>63423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>17864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32285</t>
+          <t>31933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>19312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42859</t>
+          <t>43042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56042</t>
+          <t>55927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12538</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26013</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>16827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36520</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48288</t>
+          <t>48802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29355</t>
+          <t>29381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34758</t>
+          <t>34614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43273</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40329</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>22800</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57225</t>
+          <t>58691</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>157440</t>
+          <t>157534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>177318</t>
+          <t>177725</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169496</t>
+          <t>168653</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>183533</t>
+          <t>183351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331998</t>
+          <t>330532</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>357533</t>
+          <t>356432</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>22614</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>30292</t>
+          <t>34009</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>40324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>43289</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>28210</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13817</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>31706</t>
+          <t>36274</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23710</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37183</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>48533</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>48533</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>48533</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18931</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28064</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21011</t>
+          <t>22094</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>33841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27307</t>
+          <t>29703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>53390</t>
+          <t>57197</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46106</t>
+          <t>49104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58532</t>
+          <t>62018</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37002</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37002</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37002</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>65037</t>
+          <t>69016</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65037</t>
+          <t>69016</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65037</t>
+          <t>69016</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>20931</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23398</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>37196</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29991</t>
+          <t>33892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>47769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23801</t>
+          <t>26178</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28702</t>
+          <t>31872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>64195</t>
+          <t>71407</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55756</t>
+          <t>62599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70105</t>
+          <t>77922</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>54823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>54823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49768</t>
+          <t>54823</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>79154</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>79154</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79154</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>15285</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19751</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25510</t>
+          <t>27993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>35196</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>49351</t>
+          <t>54515</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43283</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54336</t>
+          <t>59911</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>69800</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>69800</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>69800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>922</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>479</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -11425,12 +11425,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -11460,12 +11460,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -11493,27 +11493,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>17215</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11528,27 +11528,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29853</t>
+          <t>33588</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11563,27 +11563,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>47855</t>
+          <t>52945</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44490</t>
+          <t>48851</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>54346</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>37246</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61139</t>
+          <t>66343</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24561</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47614</t>
+          <t>52043</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78884</t>
+          <t>84630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>152643</t>
+          <t>170405</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137991</t>
+          <t>153568</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>164863</t>
+          <t>182665</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>215610</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>189042</t>
+          <t>205906</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203576</t>
+          <t>221520</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>350474</t>
+          <t>386015</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>333849</t>
+          <t>367461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>365119</t>
+          <t>400048</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>199130</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>412733</t>
+          <t>452091</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
